--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60103EAD-2396-414C-A57C-E266A9FEA2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B548A-71B6-419F-9C3C-4DEB9DC1CAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="74">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -54,9 +54,6 @@
     <t>ETU00ZZZZ</t>
   </si>
   <si>
-    <t>ETU00WWWW</t>
-  </si>
-  <si>
     <t>Ligne</t>
   </si>
   <si>
@@ -99,45 +96,12 @@
     <t>Index</t>
   </si>
   <si>
-    <t>Création html</t>
-  </si>
-  <si>
     <t>Affichage</t>
   </si>
   <si>
-    <t>Design css</t>
-  </si>
-  <si>
     <t>Metier</t>
   </si>
   <si>
-    <t>checkLogin</t>
-  </si>
-  <si>
-    <t>Integration</t>
-  </si>
-  <si>
-    <t>Gestion Categorie</t>
-  </si>
-  <si>
-    <t>Categorie</t>
-  </si>
-  <si>
-    <t>table login</t>
-  </si>
-  <si>
-    <t>données test</t>
-  </si>
-  <si>
-    <t>Liste</t>
-  </si>
-  <si>
-    <t>Categorie-add</t>
-  </si>
-  <si>
-    <t>Ajout</t>
-  </si>
-  <si>
     <t>Base</t>
   </si>
   <si>
@@ -181,6 +145,123 @@
   </si>
   <si>
     <t>ETU003268</t>
+  </si>
+  <si>
+    <t>ModuleCleanupPage</t>
+  </si>
+  <si>
+    <t>Creation de connection</t>
+  </si>
+  <si>
+    <t>AdminPage</t>
+  </si>
+  <si>
+    <t>Importation fichier csv</t>
+  </si>
+  <si>
+    <t>Boutton de reinitialisation</t>
+  </si>
+  <si>
+    <t>Importation image</t>
+  </si>
+  <si>
+    <t>Gestion commande</t>
+  </si>
+  <si>
+    <t>CommandeList</t>
+  </si>
+  <si>
+    <t>Affichage des liste commande</t>
+  </si>
+  <si>
+    <t>FrontOffice</t>
+  </si>
+  <si>
+    <t>Gestion Produits</t>
+  </si>
+  <si>
+    <t>ProduitList</t>
+  </si>
+  <si>
+    <t>Liste des produits + fiches</t>
+  </si>
+  <si>
+    <t>Gestion Achat</t>
+  </si>
+  <si>
+    <t>PanierManage</t>
+  </si>
+  <si>
+    <t>Faire marcher le panier</t>
+  </si>
+  <si>
+    <t>CommandeManage</t>
+  </si>
+  <si>
+    <t>Validation com (pay livraison sans frai)</t>
+  </si>
+  <si>
+    <t>Gestion de donnee</t>
+  </si>
+  <si>
+    <t>(---------)</t>
+  </si>
+  <si>
+    <t>Mise a jours des donnees dans existingApp New -&gt; ext</t>
+  </si>
+  <si>
+    <t>Mise a jours des donnees dans existingApp ext -&gt; new</t>
+  </si>
+  <si>
+    <t>Gestion de commande</t>
+  </si>
+  <si>
+    <t>Etat de commande existante : dans le panier/paiement effecuté/annulé</t>
+  </si>
+  <si>
+    <t>TableauManage</t>
+  </si>
+  <si>
+    <t>Tableau de bord (nb commande &amp; montant par jrs)</t>
+  </si>
+  <si>
+    <t>TotalCommande</t>
+  </si>
+  <si>
+    <t>Total generale</t>
+  </si>
+  <si>
+    <t>Gestion import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny  import 1 ihany ny déclinaison, fa tsisy combinaison </t>
+  </si>
+  <si>
+    <t>Gestion Utilisateur</t>
+  </si>
+  <si>
+    <t>Choix de connection (user)</t>
+  </si>
+  <si>
+    <t>Connection Anonyme</t>
+  </si>
+  <si>
+    <t>Marquer les produits selon leurs dates</t>
+  </si>
+  <si>
+    <t>Recherche Multicritere (nom, categorie,intervalle de prix)</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Boutton de modification d'etat</t>
   </si>
 </sst>
 </file>
@@ -190,7 +271,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -265,6 +346,26 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -292,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -432,11 +533,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -481,17 +593,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +631,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46154.620745601853" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46154.711536111114" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -820,7 +937,7 @@
     <pivotField name="Type" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Qui" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items count="6">
-        <item x="3"/>
+        <item n="ETU003268" x="3"/>
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -1090,23 +1207,35 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1124,42 +1253,43 @@
     <col min="1" max="1" width="5.90625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" customWidth="1"/>
+    <col min="5" max="5" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="14">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -1167,37 +1297,36 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>2</v>
+      <c r="G2" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H2" s="6">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I2" s="8">
-        <f>detail_avancement!B2</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J2" s="8">
-        <f t="shared" ref="J2:J7" si="0">H2-I2</f>
-        <v>10</v>
+        <f t="shared" ref="J2:J6" si="0">H2-I2</f>
+        <v>0</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K10" si="1">(I2/(I2+J2))</f>
-        <v>0.66666666666666663</v>
+        <f t="shared" ref="K2:K6" si="1">(I2/(I2+J2))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1">
@@ -1205,37 +1334,36 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="6">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I3" s="8">
-        <f>detail_avancement!B3</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J3" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K3" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
@@ -1243,37 +1371,36 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H4" s="6">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="I4" s="8">
-        <f>detail_avancement!B4</f>
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
@@ -1281,37 +1408,36 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H5" s="6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I5" s="8">
-        <f>detail_avancement!B5</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J5" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
@@ -1319,37 +1445,36 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H6" s="6">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="I6" s="8">
-        <f>detail_avancement!B6</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
@@ -1357,36 +1482,35 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H7" s="6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I7" s="8">
-        <f>detail_avancement!B7</f>
         <v>0</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f t="shared" ref="J7" si="2">H7-I7</f>
+        <v>30</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K7" si="3">(I7/(I7+J7))</f>
         <v>0</v>
       </c>
     </row>
@@ -1394,246 +1518,493 @@
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
+      <c r="B8" s="42" t="s">
+        <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>46</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H8" s="6">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="I8" s="8">
-        <f>detail_avancement!B8</f>
-        <v>90</v>
+        <f>detail_avancement!B7</f>
+        <v>0</v>
       </c>
       <c r="J8" s="8">
-        <v>0</v>
+        <f>H8-I8</f>
+        <v>180</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(I8/(I8+J8))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
+      <c r="B9" s="42" t="s">
+        <v>44</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>49</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H9" s="6">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="I9" s="8">
-        <f>detail_avancement!B9</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J9" s="8">
-        <v>0</v>
+        <f>H9-I9</f>
+        <v>60</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(I9/(I9+J9))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
+      <c r="B10" s="42" t="s">
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>4</v>
+        <v>52</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>34</v>
       </c>
       <c r="H10" s="6">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="I10" s="8">
-        <f>detail_avancement!B10</f>
         <v>0</v>
       </c>
       <c r="J10" s="8">
         <f>H10-I10</f>
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="1"/>
+        <f>(I10/(I10+J10))</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="6">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f>detail_avancement!B10</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <f>H11-I11</f>
+        <v>30</v>
+      </c>
+      <c r="K11" s="9">
+        <f>(I11/(I11+J11))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="A12" s="44">
+        <v>11</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="6">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <f>detail_avancement!B11</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <f>H12-I12</f>
+        <v>30</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" ref="K12" si="4">(I12/(I12+J12))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="6">
+        <v>60</v>
+      </c>
+      <c r="I13" s="8">
+        <f>detail_avancement!B12</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <f>H13-I13</f>
+        <v>60</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" ref="K13" si="5">(I13/(I13+J13))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="6">
+        <v>90</v>
+      </c>
+      <c r="I14" s="8">
+        <f>detail_avancement!B13</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <f>H14-I14</f>
+        <v>90</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" ref="K14" si="6">(I14/(I14+J14))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="6">
+        <v>40</v>
+      </c>
+      <c r="I15" s="8">
+        <f>detail_avancement!B14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <f>H15-I15</f>
+        <v>40</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" ref="K15" si="7">(I15/(I15+J15))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="6">
+        <v>120</v>
+      </c>
+      <c r="I16" s="8">
+        <f>detail_avancement!B15</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
+        <f>H16-I16</f>
+        <v>120</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" ref="K16" si="8">(I16/(I16+J16))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="6">
+        <v>70</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <f>H17-I17</f>
+        <v>70</v>
+      </c>
+      <c r="K17" s="9">
+        <f>(I17/(I17+J17))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="A18" s="10">
+        <v>17</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="6">
+        <v>70</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <f>H18-I18</f>
+        <v>70</v>
+      </c>
+      <c r="K18" s="9">
+        <f>(I18/(I18+J18))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-    </row>
-    <row r="20" spans="1:11" ht="12.5">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="6">
+        <v>120</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <f>H19-I19</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="9">
+        <f>(I19/(I19+J19))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14">
+      <c r="A20" s="10">
+        <v>19</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="6">
+        <v>140</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <f>H20-I20</f>
+        <v>140</v>
+      </c>
+      <c r="K20" s="9">
+        <f>(I20/(I20+J20))</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1648,92 +2019,92 @@
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="24"/>
       <c r="B1" s="25" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C1" s="26"/>
       <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="30">
+        <v>34</v>
+      </c>
+      <c r="B3" s="32">
         <v>35</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="33">
         <v>30</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="34">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="34">
+      <c r="A4" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="35">
         <v>50</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>10</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="37">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <v>40</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <v>110</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="37">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <v>60</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <v>10</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36"/>
+      <c r="A7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="37" t="s">
-        <v>45</v>
+      <c r="A8" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="B8" s="38">
         <v>185</v>
@@ -1745,13 +2116,13 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="13">
       <c r="A12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.55172413793103448</v>
+        <v>0.23958333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -1776,41 +2147,41 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>185</v>
+        <v>1920</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>130</v>
+        <v>1460</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.55172413793103448</v>
+        <v>0.23958333333333334</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
-        <v>0.56756756756756754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -1818,10 +2189,10 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>2.1666666666666665</v>
+        <v>24.333333333333332</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E3" s="18"/>
     </row>
@@ -1840,10 +2211,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C1" s="21">
         <v>46048</v>
@@ -1861,12 +2232,10 @@
       </c>
       <c r="B2" s="15">
         <f t="shared" ref="B2:B10" si="0">SUM(D2:P2)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C2" s="18"/>
-      <c r="D2" s="22">
-        <v>20</v>
-      </c>
+      <c r="D2" s="22"/>
       <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -1887,14 +2256,10 @@
       </c>
       <c r="B4" s="15">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C4" s="22">
-        <v>20</v>
-      </c>
-      <c r="D4" s="22">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
@@ -1915,12 +2280,10 @@
       </c>
       <c r="B6" s="15">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="23">
-        <v>10</v>
-      </c>
+      <c r="D6" s="23"/>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
@@ -1941,12 +2304,10 @@
       </c>
       <c r="B8" s="15">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C8" s="18"/>
-      <c r="D8" s="23">
-        <v>90</v>
-      </c>
+      <c r="D8" s="23"/>
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
@@ -1955,11 +2316,9 @@
       </c>
       <c r="B9" s="15">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="D9" s="11">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="11">

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B548A-71B6-419F-9C3C-4DEB9DC1CAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FF26FA-E42D-4535-86EA-3BF461284353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Boutton de modification d'etat</t>
+  </si>
+  <si>
+    <t>ETU0032682</t>
   </si>
 </sst>
 </file>
@@ -595,6 +598,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -604,11 +612,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46154.711536111114" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46154.901287384258" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -652,25 +655,26 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Qui" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
-        <s v="ETU00YYYY"/>
-        <s v="ETU00XXXX"/>
-        <s v="ETU00ZZZZ"/>
-        <s v="ETU00WWWW"/>
+      <sharedItems containsBlank="1" count="6">
+        <s v="ETU003268"/>
         <m/>
+        <s v="ETU00YYYY" u="1"/>
+        <s v="ETU00XXXX" u="1"/>
+        <s v="ETU00ZZZZ" u="1"/>
+        <s v="ETU00WWWW" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="50"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="10" maxValue="360"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="90"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="360"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="40"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="240"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -687,108 +691,228 @@
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
     <s v="Index"/>
-    <s v="Création html"/>
-    <s v="Affichage"/>
-    <x v="0"/>
-    <n v="30"/>
-    <n v="20"/>
-    <n v="10"/>
-    <n v="0.66666666666666663"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Login"/>
-    <s v="Index"/>
-    <s v="Design css"/>
-    <s v="Metier"/>
-    <x v="1"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="20"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Login"/>
-    <s v="Index"/>
-    <s v="checkLogin"/>
-    <s v="Integration"/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="10"/>
-    <n v="20"/>
-    <n v="0.33333333333333331"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie"/>
-    <s v="table login"/>
-    <s v="Affichage"/>
-    <x v="2"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie"/>
-    <s v="données test"/>
-    <s v="Metier"/>
-    <x v="2"/>
-    <n v="50"/>
-    <n v="10"/>
-    <n v="40"/>
-    <n v="0.2"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie"/>
-    <s v="Liste"/>
-    <s v="Integration"/>
-    <x v="3"/>
-    <n v="25"/>
-    <n v="0"/>
-    <n v="25"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie-add"/>
-    <s v="Ajout"/>
+    <s v="Creation de connection"/>
     <s v="Affichage"/>
     <x v="0"/>
     <n v="10"/>
-    <n v="90"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie-add"/>
-    <s v="Ajout"/>
+    <s v="Gestion de donnee"/>
+    <s v="ModuleCleanupPage"/>
+    <s v="Boutton de reinitialisation"/>
     <s v="Metier"/>
-    <x v="3"/>
-    <n v="5"/>
-    <n v="30"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
     <n v="0"/>
     <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Categorie"/>
-    <s v="Categorie-add"/>
-    <s v="Ajout"/>
+    <s v="Gestion de donnee"/>
+    <s v="AdminPage"/>
+    <s v="Importation fichier csv"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="360"/>
+    <n v="360"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de donnee"/>
+    <s v="AdminPage"/>
+    <s v="Importation image"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion commande"/>
+    <s v="CommandeList"/>
+    <s v="Affichage des liste commande"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="180"/>
+    <n v="0"/>
+    <n v="180"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion commande"/>
+    <s v="CommandeList"/>
+    <s v="Boutton de modification d'etat"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produits"/>
+    <s v="ProduitList"/>
+    <s v="Liste des produits + fiches"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="180"/>
+    <n v="0"/>
+    <n v="180"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Achat"/>
+    <s v="PanierManage"/>
+    <s v="Faire marcher le panier"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion commande"/>
+    <s v="CommandeManage"/>
+    <s v="Validation com (pay livraison sans frai)"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="240"/>
+    <n v="0"/>
+    <n v="240"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de donnee"/>
+    <s v="(---------)"/>
+    <s v="Mise a jours des donnees dans existingApp New -&gt; ext"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de donnee"/>
+    <s v="(---------)"/>
+    <s v="Mise a jours des donnees dans existingApp ext -&gt; new"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="30"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de commande"/>
+    <s v="(---------)"/>
+    <s v="Etat de commande existante : dans le panier/paiement effecuté/annulé"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de commande"/>
+    <s v="TableauManage"/>
+    <s v="Tableau de bord (nb commande &amp; montant par jrs)"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="90"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de commande"/>
+    <s v="TotalCommande"/>
+    <s v="Total generale"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion import"/>
+    <s v="(---------)"/>
+    <s v="Ny  import 1 ihany ny déclinaison, fa tsisy combinaison "/>
     <s v="Base"/>
-    <x v="3"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="5"/>
+    <x v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="Index"/>
+    <s v="Choix de connection (user)"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="70"/>
+    <n v="0"/>
+    <n v="70"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="Index"/>
+    <s v="Connection Anonyme"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="70"/>
+    <n v="0"/>
+    <n v="70"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produits"/>
+    <s v="ProduitList"/>
+    <s v="Marquer les produits selon leurs dates"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produits"/>
+    <s v="ProduitList"/>
+    <s v="Recherche Multicritere (nom, categorie,intervalle de prix)"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="140"/>
+    <n v="0"/>
+    <n v="140"/>
     <n v="0"/>
   </r>
   <r>
@@ -797,127 +921,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="4"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -928,7 +932,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0">
-  <location ref="A1:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A1:D5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField name="Catégorie" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Module" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -936,12 +940,13 @@
     <pivotField name="Description tâche" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Type" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Qui" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items count="6">
-        <item n="ETU003268" x="3"/>
+      <items count="7">
+        <item n="ETU003268" m="1" x="5"/>
+        <item n="ETU0032682" x="0"/>
+        <item m="1" x="3"/>
+        <item m="1" x="2"/>
+        <item m="1" x="4"/>
         <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -953,21 +958,12 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="1"/>
     </i>
     <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -1217,7 +1213,7 @@
       <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="36" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1225,7 +1221,7 @@
       <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="36" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1233,7 +1229,7 @@
       <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="36" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1311,7 +1307,7 @@
       <c r="F2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H2" s="6">
@@ -1348,7 +1344,7 @@
       <c r="F3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="6">
@@ -1385,7 +1381,7 @@
       <c r="F4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H4" s="6">
@@ -1422,7 +1418,7 @@
       <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="6">
@@ -1450,7 +1446,7 @@
       <c r="C6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="32" t="s">
         <v>42</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -1459,22 +1455,22 @@
       <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="6">
         <v>180</v>
       </c>
       <c r="I6" s="8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
@@ -1487,7 +1483,7 @@
       <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="32" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -1496,35 +1492,35 @@
       <c r="F7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="6">
         <v>30</v>
       </c>
       <c r="I7" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J7" s="8">
         <f t="shared" ref="J7" si="2">H7-I7</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" ref="K7" si="3">(I7/(I7+J7))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="34" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -1533,36 +1529,35 @@
       <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="6">
         <v>180</v>
       </c>
       <c r="I8" s="8">
-        <f>detail_avancement!B7</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J8" s="8">
-        <f>H8-I8</f>
-        <v>180</v>
+        <f t="shared" ref="J8:J20" si="4">H8-I8</f>
+        <v>0</v>
       </c>
       <c r="K8" s="9">
         <f>(I8/(I8+J8))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="34" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1571,7 +1566,7 @@
       <c r="F9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="6">
@@ -1581,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="8">
-        <f>H9-I9</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K9" s="9">
@@ -1593,13 +1588,13 @@
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="34" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -1608,7 +1603,7 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="6">
@@ -1618,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="8">
-        <f>H10-I10</f>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="K10" s="9">
@@ -1630,13 +1625,13 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -1645,7 +1640,7 @@
       <c r="F11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="6">
@@ -1656,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="8">
-        <f>H11-I11</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="K11" s="9">
@@ -1665,16 +1660,16 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="44">
+      <c r="A12" s="35">
         <v>11</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -1683,7 +1678,7 @@
       <c r="F12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="6">
@@ -1694,11 +1689,11 @@
         <v>0</v>
       </c>
       <c r="J12" s="8">
-        <f>H12-I12</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" ref="K12" si="4">(I12/(I12+J12))</f>
+        <f t="shared" ref="K12" si="5">(I12/(I12+J12))</f>
         <v>0</v>
       </c>
     </row>
@@ -1706,13 +1701,13 @@
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -1721,7 +1716,7 @@
       <c r="F13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="6">
@@ -1732,11 +1727,11 @@
         <v>0</v>
       </c>
       <c r="J13" s="8">
-        <f>H13-I13</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" ref="K13" si="5">(I13/(I13+J13))</f>
+        <f t="shared" ref="K13" si="6">(I13/(I13+J13))</f>
         <v>0</v>
       </c>
     </row>
@@ -1744,13 +1739,13 @@
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="34" t="s">
         <v>59</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -1759,7 +1754,7 @@
       <c r="F14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H14" s="6">
@@ -1770,11 +1765,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <f>H14-I14</f>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" ref="K14" si="6">(I14/(I14+J14))</f>
+        <f t="shared" ref="K14" si="7">(I14/(I14+J14))</f>
         <v>0</v>
       </c>
     </row>
@@ -1782,13 +1777,13 @@
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="34" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="7" t="s">
@@ -1797,7 +1792,7 @@
       <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="6">
@@ -1808,11 +1803,11 @@
         <v>0</v>
       </c>
       <c r="J15" s="8">
-        <f>H15-I15</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" ref="K15" si="7">(I15/(I15+J15))</f>
+        <f t="shared" ref="K15" si="8">(I15/(I15+J15))</f>
         <v>0</v>
       </c>
     </row>
@@ -1820,22 +1815,22 @@
       <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="34" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="6">
@@ -1846,11 +1841,11 @@
         <v>0</v>
       </c>
       <c r="J16" s="8">
-        <f>H16-I16</f>
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" ref="K16" si="8">(I16/(I16+J16))</f>
+        <f t="shared" ref="K16" si="9">(I16/(I16+J16))</f>
         <v>0</v>
       </c>
     </row>
@@ -1858,13 +1853,13 @@
       <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="34" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -1873,7 +1868,7 @@
       <c r="F17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="6">
@@ -1883,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="8">
-        <f>H17-I17</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="K17" s="9">
@@ -1895,13 +1890,13 @@
       <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="34" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -1910,7 +1905,7 @@
       <c r="F18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="6">
@@ -1920,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="8">
-        <f>H18-I18</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="K18" s="9">
@@ -1932,13 +1927,13 @@
       <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="34" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -1947,7 +1942,7 @@
       <c r="F19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H19" s="6">
@@ -1957,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="8">
-        <f>H19-I19</f>
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="K19" s="9">
@@ -1969,13 +1964,13 @@
       <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="34" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -1984,7 +1979,7 @@
       <c r="F20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="G20" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="6">
@@ -1994,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="8">
-        <f>H20-I20</f>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="K20" s="9">
@@ -2040,80 +2035,38 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="32">
-        <v>35</v>
-      </c>
-      <c r="C3" s="33">
-        <v>30</v>
-      </c>
-      <c r="D3" s="34">
-        <v>30</v>
+        <v>74</v>
+      </c>
+      <c r="B3" s="37">
+        <v>1920</v>
+      </c>
+      <c r="C3" s="38">
+        <v>460</v>
+      </c>
+      <c r="D3" s="39">
+        <v>1460</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="35">
-        <v>50</v>
-      </c>
-      <c r="C4" s="36">
-        <v>10</v>
-      </c>
-      <c r="D4" s="37">
-        <v>40</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="35">
-        <v>40</v>
-      </c>
-      <c r="C5" s="36">
-        <v>110</v>
-      </c>
-      <c r="D5" s="37">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="35">
-        <v>60</v>
-      </c>
-      <c r="C6" s="36">
-        <v>10</v>
-      </c>
-      <c r="D6" s="37">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="38">
-        <v>185</v>
-      </c>
-      <c r="C8" s="39">
-        <v>160</v>
-      </c>
-      <c r="D8" s="40">
-        <v>130</v>
+      <c r="B5" s="43">
+        <v>1920</v>
+      </c>
+      <c r="C5" s="44">
+        <v>460</v>
+      </c>
+      <c r="D5" s="45">
+        <v>1460</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2122,7 +2075,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.23958333333333334</v>
+        <v>0.41145833333333331</v>
       </c>
     </row>
   </sheetData>
@@ -2169,15 +2122,15 @@
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>460</v>
+        <v>790</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>1460</v>
+        <v>1130</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.23958333333333334</v>
+        <v>0.41145833333333331</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2189,7 +2142,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>24.333333333333332</v>
+        <v>18.833333333333332</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FF26FA-E42D-4535-86EA-3BF461284353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E619CB24-03FB-4A65-A9E8-012719C54121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46154.901287384258" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46155.439080324075" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -674,7 +674,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="240"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -743,9 +743,9 @@
     <s v="Affichage"/>
     <x v="0"/>
     <n v="180"/>
-    <n v="0"/>
-    <n v="180"/>
-    <n v="0"/>
+    <n v="120"/>
+    <n v="60"/>
+    <n v="0.66666666666666663"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -755,9 +755,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="30"/>
-    <n v="0"/>
     <n v="30"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -767,9 +767,9 @@
     <s v="Affichage"/>
     <x v="0"/>
     <n v="180"/>
-    <n v="0"/>
     <n v="180"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -2041,10 +2041,10 @@
         <v>1920</v>
       </c>
       <c r="C3" s="38">
-        <v>460</v>
+        <v>790</v>
       </c>
       <c r="D3" s="39">
-        <v>1460</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -2063,10 +2063,10 @@
         <v>1920</v>
       </c>
       <c r="C5" s="44">
-        <v>460</v>
+        <v>790</v>
       </c>
       <c r="D5" s="45">
-        <v>1460</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E619CB24-03FB-4A65-A9E8-012719C54121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0ADDA1-C363-40D8-9F8D-8ACB7D0D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46155.439080324075" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46155.934006828706" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -1573,15 +1573,15 @@
         <v>60</v>
       </c>
       <c r="I9" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J9" s="8">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K9" s="9">
         <f>(I9/(I9+J9))</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
@@ -1607,18 +1607,18 @@
         <v>34</v>
       </c>
       <c r="H10" s="6">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="I10" s="8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J10" s="8">
         <f t="shared" si="4"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9">
         <f>(I10/(I10+J10))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
@@ -1644,19 +1644,18 @@
         <v>34</v>
       </c>
       <c r="H11" s="6">
-        <v>30</v>
-      </c>
-      <c r="I11" s="8">
-        <f>detail_avancement!B10</f>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="I11" s="6">
+        <v>10</v>
       </c>
       <c r="J11" s="8">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9">
         <f>(I11/(I11+J11))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
@@ -1682,19 +1681,18 @@
         <v>34</v>
       </c>
       <c r="H12" s="6">
-        <v>30</v>
-      </c>
-      <c r="I12" s="8">
-        <f>detail_avancement!B11</f>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="I12" s="6">
+        <v>10</v>
       </c>
       <c r="J12" s="8">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" ref="K12" si="5">(I12/(I12+J12))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
@@ -1875,15 +1873,15 @@
         <v>70</v>
       </c>
       <c r="I17" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J17" s="8">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K17" s="9">
         <f>(I17/(I17+J17))</f>
-        <v>0</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
@@ -2075,7 +2073,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.41145833333333331</v>
+        <v>0.54385964912280704</v>
       </c>
     </row>
   </sheetData>
@@ -2118,19 +2116,19 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1920</v>
+        <v>1710</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>790</v>
+        <v>930</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>1130</v>
+        <v>780</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.41145833333333331</v>
+        <v>0.54385964912280704</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2142,7 +2140,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>18.833333333333332</v>
+        <v>13</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0ADDA1-C363-40D8-9F8D-8ACB7D0D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78803127-2EA9-46F5-AA4B-78B07E0CDF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46155.934006828706" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46156.230681712965" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -671,7 +671,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="360"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="240"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="140"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1"/>
@@ -779,9 +779,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="60"/>
-    <n v="0"/>
-    <n v="60"/>
-    <n v="0"/>
+    <n v="20"/>
+    <n v="40"/>
+    <n v="0.33333333333333331"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -790,10 +790,10 @@
     <s v="Validation com (pay livraison sans frai)"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="240"/>
+    <n v="70"/>
+    <n v="70"/>
     <n v="0"/>
-    <n v="240"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -802,10 +802,10 @@
     <s v="Mise a jours des donnees dans existingApp New -&gt; ext"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="30"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
-    <n v="30"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -814,10 +814,10 @@
     <s v="Mise a jours des donnees dans existingApp ext -&gt; new"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="30"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
-    <n v="30"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -875,9 +875,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="70"/>
-    <n v="0"/>
-    <n v="70"/>
-    <n v="0"/>
+    <n v="30"/>
+    <n v="40"/>
+    <n v="0.42857142857142855"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -2036,13 +2036,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="37">
-        <v>1920</v>
+        <v>1710</v>
       </c>
       <c r="C3" s="38">
-        <v>790</v>
+        <v>930</v>
       </c>
       <c r="D3" s="39">
-        <v>1130</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -2058,13 +2058,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="43">
-        <v>1920</v>
+        <v>1710</v>
       </c>
       <c r="C5" s="44">
-        <v>790</v>
+        <v>930</v>
       </c>
       <c r="D5" s="45">
-        <v>1130</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78803127-2EA9-46F5-AA4B-78B07E0CDF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABB5833-ABCD-4B9B-8C2A-A52FF7497EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46156.230681712965" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46156.923465972221" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABB5833-ABCD-4B9B-8C2A-A52FF7497EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FFCFA2-F6B9-40DE-8923-A6EBC001ED11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46156.923465972221" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46157.182008912037" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -1570,18 +1570,18 @@
         <v>34</v>
       </c>
       <c r="H9" s="6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I9" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J9" s="8">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9">
         <f>(I9/(I9+J9))</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
@@ -1870,18 +1870,18 @@
         <v>34</v>
       </c>
       <c r="H17" s="6">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I17" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J17" s="8">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K17" s="9">
         <f>(I17/(I17+J17))</f>
-        <v>0.42857142857142855</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
@@ -1907,18 +1907,18 @@
         <v>34</v>
       </c>
       <c r="H18" s="6">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I18" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J18" s="8">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K18" s="9">
         <f>(I18/(I18+J18))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
@@ -1944,18 +1944,18 @@
         <v>34</v>
       </c>
       <c r="H19" s="6">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I19" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J19" s="8">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K19" s="9">
         <f>(I19/(I19+J19))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="14">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.54385964912280704</v>
+        <v>0.66883116883116878</v>
       </c>
     </row>
   </sheetData>
@@ -2116,19 +2116,19 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1710</v>
+        <v>1540</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>930</v>
+        <v>1030</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>780</v>
+        <v>510</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.54385964912280704</v>
+        <v>0.66883116883116878</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2140,7 +2140,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FFCFA2-F6B9-40DE-8923-A6EBC001ED11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492D4AA2-4752-4CB0-936A-D60E483374BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -265,6 +265,42 @@
   </si>
   <si>
     <t>ETU0032682</t>
+  </si>
+  <si>
+    <t>Gestion Donnee</t>
+  </si>
+  <si>
+    <t>(--------)</t>
+  </si>
+  <si>
+    <t>Verification colonne</t>
+  </si>
+  <si>
+    <t>Verification date</t>
+  </si>
+  <si>
+    <t>Montant positif</t>
+  </si>
+  <si>
+    <t>Gestion Stock</t>
+  </si>
+  <si>
+    <t>StockPages</t>
+  </si>
+  <si>
+    <t>Afficher les quantites en stocks</t>
+  </si>
+  <si>
+    <t>Backoffice/FrontOffice</t>
+  </si>
+  <si>
+    <t>(-----------)</t>
+  </si>
+  <si>
+    <t>Integration/Test</t>
+  </si>
+  <si>
+    <t>Metier/Affichage</t>
   </si>
 </sst>
 </file>
@@ -634,7 +670,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46157.182008912037" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46157.764618402776" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -778,10 +814,10 @@
     <s v="Faire marcher le panier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="60"/>
-    <n v="20"/>
-    <n v="40"/>
-    <n v="0.33333333333333331"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -874,10 +910,10 @@
     <s v="Choix de connection (user)"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="70"/>
-    <n v="30"/>
-    <n v="40"/>
-    <n v="0.42857142857142855"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -886,10 +922,10 @@
     <s v="Connection Anonyme"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="70"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="70"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -898,10 +934,10 @@
     <s v="Marquer les produits selon leurs dates"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="120"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="120"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -1243,11 +1279,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="19.90625" customWidth="1"/>
     <col min="5" max="5" width="20.7265625" customWidth="1"/>
@@ -1992,6 +2028,191 @@
       </c>
       <c r="K20" s="9">
         <f>(I20/(I20+J20))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="6">
+        <v>10</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" ref="J21:J24" si="10">H21-I21</f>
+        <v>10</v>
+      </c>
+      <c r="K21" s="9">
+        <f>(I21/(I21+J21))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>21</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="6">
+        <v>5</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="K22" s="9">
+        <f>(I22/(I22+J22))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="6">
+        <v>5</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="K23" s="9">
+        <f>(I23/(I23+J23))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>23</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="6">
+        <v>40</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="10"/>
+        <v>40</v>
+      </c>
+      <c r="K24" s="9">
+        <f>(I24/(I24+J24))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>24</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="6">
+        <v>60</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" ref="J25" si="11">H25-I25</f>
+        <v>60</v>
+      </c>
+      <c r="K25" s="9">
+        <f>(I25/(I25+J25))</f>
         <v>0</v>
       </c>
     </row>
@@ -2036,13 +2257,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="37">
-        <v>1710</v>
+        <v>1540</v>
       </c>
       <c r="C3" s="38">
-        <v>930</v>
+        <v>1030</v>
       </c>
       <c r="D3" s="39">
-        <v>780</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -2058,13 +2279,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="43">
-        <v>1710</v>
+        <v>1540</v>
       </c>
       <c r="C5" s="44">
-        <v>930</v>
+        <v>1030</v>
       </c>
       <c r="D5" s="45">
-        <v>780</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2073,7 +2294,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.66883116883116878</v>
+        <v>0.62048192771084343</v>
       </c>
     </row>
   </sheetData>
@@ -2116,7 +2337,7 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1540</v>
+        <v>1660</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
@@ -2124,11 +2345,11 @@
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>510</v>
+        <v>630</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.66883116883116878</v>
+        <v>0.62048192771084343</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2140,7 +2361,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492D4AA2-4752-4CB0-936A-D60E483374BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64161726-7A33-4770-BB8B-5AB9467A7BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,7 +670,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46157.764618402776" refreshedVersion="8" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46158.274117939814" refreshedVersion="8" recordCount="25" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -701,7 +701,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="10" maxValue="360"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="360"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="360"/>
@@ -722,7 +722,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="20">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="25">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -949,6 +949,66 @@
     <n v="140"/>
     <n v="0"/>
     <n v="140"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Donnee"/>
+    <s v="(--------)"/>
+    <s v="Verification colonne"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Donnee"/>
+    <s v="(--------)"/>
+    <s v="Verification date"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Donnee"/>
+    <s v="(--------)"/>
+    <s v="Montant positif"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Stock"/>
+    <s v="StockPages"/>
+    <s v="Afficher les quantites en stocks"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice/FrontOffice"/>
+    <s v="(---------)"/>
+    <s v="(-----------)"/>
+    <s v="Integration/Test"/>
+    <s v="Metier/Affichage"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
     <n v="0"/>
   </r>
   <r>
@@ -1754,19 +1814,18 @@
         <v>34</v>
       </c>
       <c r="H13" s="6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I13" s="8">
-        <f>detail_avancement!B12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J13" s="8">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" ref="K13" si="6">(I13/(I13+J13))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
@@ -1916,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <f>(I17/(I17+J17))</f>
+        <f t="shared" ref="K17:K25" si="10">(I17/(I17+J17))</f>
         <v>1</v>
       </c>
     </row>
@@ -1953,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="9">
-        <f>(I18/(I18+J18))</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -1990,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="9">
-        <f>(I19/(I19+J19))</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -2020,15 +2079,15 @@
         <v>140</v>
       </c>
       <c r="I20" s="8">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J20" s="8">
         <f t="shared" si="4"/>
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9">
-        <f>(I20/(I20+J20))</f>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
@@ -2057,15 +2116,15 @@
         <v>10</v>
       </c>
       <c r="I21" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" ref="J21:J24" si="10">H21-I21</f>
-        <v>10</v>
+        <f t="shared" ref="J21:J24" si="11">H21-I21</f>
+        <v>0</v>
       </c>
       <c r="K21" s="9">
-        <f>(I21/(I21+J21))</f>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
@@ -2094,15 +2153,15 @@
         <v>5</v>
       </c>
       <c r="I22" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J22" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="K22" s="9">
-        <f>(I22/(I22+J22))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
@@ -2131,15 +2190,15 @@
         <v>5</v>
       </c>
       <c r="I23" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="K23" s="9">
-        <f>(I23/(I23+J23))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
@@ -2171,11 +2230,11 @@
         <v>0</v>
       </c>
       <c r="J24" s="8">
+        <f t="shared" si="11"/>
+        <v>40</v>
+      </c>
+      <c r="K24" s="9">
         <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="K24" s="9">
-        <f>(I24/(I24+J24))</f>
         <v>0</v>
       </c>
     </row>
@@ -2208,11 +2267,11 @@
         <v>0</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" ref="J25" si="11">H25-I25</f>
+        <f t="shared" ref="J25" si="12">H25-I25</f>
         <v>60</v>
       </c>
       <c r="K25" s="9">
-        <f>(I25/(I25+J25))</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2257,13 +2316,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="37">
-        <v>1540</v>
+        <v>1660</v>
       </c>
       <c r="C3" s="38">
         <v>1030</v>
       </c>
       <c r="D3" s="39">
-        <v>510</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -2279,13 +2338,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="43">
-        <v>1540</v>
+        <v>1660</v>
       </c>
       <c r="C5" s="44">
         <v>1030</v>
       </c>
       <c r="D5" s="45">
-        <v>510</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2294,7 +2353,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.62048192771084343</v>
+        <v>0.74846625766871167</v>
       </c>
     </row>
   </sheetData>
@@ -2337,19 +2396,19 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1660</v>
+        <v>1630</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>1030</v>
+        <v>1220</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>630</v>
+        <v>410</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.62048192771084343</v>
+        <v>0.74846625766871167</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2361,7 +2420,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>10.5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64161726-7A33-4770-BB8B-5AB9467A7BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7060DC-6CAF-4B36-9226-890FFF067A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="87">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -291,16 +291,16 @@
     <t>Afficher les quantites en stocks</t>
   </si>
   <si>
-    <t>Backoffice/FrontOffice</t>
-  </si>
-  <si>
-    <t>(-----------)</t>
-  </si>
-  <si>
-    <t>Integration/Test</t>
-  </si>
-  <si>
-    <t>Metier/Affichage</t>
+    <t>StockPagesAdd</t>
+  </si>
+  <si>
+    <t>Page d'ajout de stock de produit</t>
+  </si>
+  <si>
+    <t>DashBoardStock</t>
+  </si>
+  <si>
+    <t>Rajout d'un tableau sur l’évolution du stock journalier d’un produit</t>
   </si>
 </sst>
 </file>
@@ -1339,14 +1339,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
     <col min="2" max="2" width="21.08984375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="19.90625" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" customWidth="1"/>
+    <col min="5" max="5" width="51.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14">
@@ -2212,29 +2212,29 @@
         <v>80</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I24" s="8">
         <v>0</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="11"/>
-        <v>40</v>
+        <f t="shared" ref="J24" si="12">H24-I24</f>
+        <v>60</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K24" si="13">(I24/(I24+J24))</f>
         <v>0</v>
       </c>
     </row>
@@ -2243,19 +2243,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="E25" s="33" t="s">
+        <v>86</v>
+      </c>
       <c r="F25" s="7" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="G25" s="32" t="s">
         <v>34</v>
@@ -2267,11 +2267,48 @@
         <v>0</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" ref="J25" si="12">H25-I25</f>
+        <f t="shared" ref="J25" si="14">H25-I25</f>
         <v>60</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K25" si="15">(I25/(I25+J25))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="6">
+        <v>40</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
+        <f>H26-I26</f>
+        <v>40</v>
+      </c>
+      <c r="K26" s="9">
+        <f>(I26/(I26+J26))</f>
         <v>0</v>
       </c>
     </row>
@@ -2353,7 +2390,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.74846625766871167</v>
+        <v>0.72189349112426038</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2433,7 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1630</v>
+        <v>1690</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
@@ -2404,11 +2441,11 @@
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.74846625766871167</v>
+        <v>0.72189349112426038</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2420,7 +2457,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>6.833333333333333</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7060DC-6CAF-4B36-9226-890FFF067A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45C154D-C5BB-47AB-BA69-43AECA5624E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Rajout d'un tableau sur l’évolution du stock journalier d’un produit</t>
+  </si>
+  <si>
+    <t>Etat de Stock pour chaque clients</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1342,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
@@ -2309,6 +2312,43 @@
       </c>
       <c r="K26" s="9">
         <f>(I26/(I26+J26))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>26</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="6">
+        <v>60</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <f>H27-I27</f>
+        <v>60</v>
+      </c>
+      <c r="K27" s="9">
+        <f>(I27/(I27+J27))</f>
         <v>0</v>
       </c>
     </row>
@@ -2390,7 +2430,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.72189349112426038</v>
+        <v>0.69714285714285718</v>
       </c>
     </row>
   </sheetData>
@@ -2433,7 +2473,7 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1690</v>
+        <v>1750</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
@@ -2441,11 +2481,11 @@
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.72189349112426038</v>
+        <v>0.69714285714285718</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2457,7 +2497,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>7.833333333333333</v>
+        <v>8.8333333333333339</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45C154D-C5BB-47AB-BA69-43AECA5624E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F27EB7-7B8C-4235-8258-9EBB989B89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,7 +409,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,6 +432,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF95DCF7"/>
         <bgColor rgb="FF95DCF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -590,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -651,6 +657,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,7 +682,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46158.274117939814" refreshedVersion="8" recordCount="25" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46158.985955439814" refreshedVersion="8" recordCount="27" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -710,7 +719,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="360"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="140"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="120"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1"/>
@@ -725,7 +734,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="25">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -865,10 +874,10 @@
     <s v="Etat de commande existante : dans le panier/paiement effecuté/annulé"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="60"/>
-    <n v="0"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -950,9 +959,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="140"/>
-    <n v="0"/>
     <n v="140"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -962,9 +971,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="10"/>
-    <n v="0"/>
     <n v="10"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -974,9 +983,9 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="0"/>
     <n v="5"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -986,8 +995,32 @@
     <s v="Metier"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="0"/>
     <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Stock"/>
+    <s v="StockPagesAdd"/>
+    <s v="Page d'ajout de stock de produit"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Stock"/>
+    <s v="DashBoardStock"/>
+    <s v="Rajout d'un tableau sur l’évolution du stock journalier d’un produit"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
     <n v="0"/>
   </r>
   <r>
@@ -1003,11 +1036,11 @@
     <n v="0"/>
   </r>
   <r>
-    <s v="Backoffice/FrontOffice"/>
-    <s v="(---------)"/>
-    <s v="(-----------)"/>
-    <s v="Integration/Test"/>
-    <s v="Metier/Affichage"/>
+    <s v="FrontOffice"/>
+    <s v="Gestion Stock"/>
+    <s v="StockPages"/>
+    <s v="Etat de Stock pour chaque clients"/>
+    <s v="Metier"/>
     <x v="0"/>
     <n v="60"/>
     <n v="0"/>
@@ -1857,16 +1890,15 @@
         <v>90</v>
       </c>
       <c r="I14" s="8">
-        <f>detail_avancement!B13</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J14" s="8">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="K14" s="9">
         <f t="shared" ref="K14" si="7">(I14/(I14+J14))</f>
-        <v>0</v>
+        <v>0.88888888888888884</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
@@ -1892,19 +1924,18 @@
         <v>34</v>
       </c>
       <c r="H15" s="6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I15" s="8">
-        <f>detail_avancement!B14</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J15" s="8">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9">
         <f t="shared" ref="K15" si="8">(I15/(I15+J15))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
@@ -1932,7 +1963,7 @@
       <c r="H16" s="6">
         <v>120</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="46">
         <f>detail_avancement!B15</f>
         <v>0</v>
       </c>
@@ -1978,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" ref="K17:K25" si="10">(I17/(I17+J17))</f>
+        <f t="shared" ref="K17:K23" si="10">(I17/(I17+J17))</f>
         <v>1</v>
       </c>
     </row>
@@ -2122,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" ref="J21:J24" si="11">H21-I21</f>
+        <f t="shared" ref="J21:J23" si="11">H21-I21</f>
         <v>0</v>
       </c>
       <c r="K21" s="9">
@@ -2227,18 +2258,18 @@
         <v>34</v>
       </c>
       <c r="H24" s="6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I24" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J24" s="8">
         <f t="shared" ref="J24" si="12">H24-I24</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" ref="K24" si="13">(I24/(I24+J24))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
@@ -2266,7 +2297,7 @@
       <c r="H25" s="6">
         <v>60</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="46">
         <v>0</v>
       </c>
       <c r="J25" s="8">
@@ -2304,15 +2335,15 @@
         <v>40</v>
       </c>
       <c r="I26" s="8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J26" s="8">
         <f>H26-I26</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9">
         <f>(I26/(I26+J26))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
@@ -2338,18 +2369,18 @@
         <v>34</v>
       </c>
       <c r="H27" s="6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I27" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J27" s="8">
         <f>H27-I27</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K27" s="9">
         <f>(I27/(I27+J27))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2393,13 +2424,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="37">
-        <v>1660</v>
+        <v>1750</v>
       </c>
       <c r="C3" s="38">
-        <v>1030</v>
+        <v>1220</v>
       </c>
       <c r="D3" s="39">
-        <v>630</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -2415,13 +2446,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="43">
-        <v>1660</v>
+        <v>1750</v>
       </c>
       <c r="C5" s="44">
-        <v>1030</v>
+        <v>1220</v>
       </c>
       <c r="D5" s="45">
-        <v>630</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2430,7 +2461,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.69714285714285718</v>
+        <v>0.8493975903614458</v>
       </c>
     </row>
   </sheetData>
@@ -2473,19 +2504,19 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1750</v>
+        <v>1660</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>1220</v>
+        <v>1410</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>530</v>
+        <v>250</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.69714285714285718</v>
+        <v>0.8493975903614458</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2497,7 +2528,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>8.8333333333333339</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F27EB7-7B8C-4235-8258-9EBB989B89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9549E906-BCBC-4614-854B-149B8B691913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="91">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>Etat de Stock pour chaque clients</t>
+  </si>
+  <si>
+    <t>Generale</t>
+  </si>
+  <si>
+    <t>(------)</t>
+  </si>
+  <si>
+    <t>Debug generale</t>
   </si>
 </sst>
 </file>
@@ -409,7 +418,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +446,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -648,6 +663,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -657,7 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -682,7 +700,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46158.985955439814" refreshedVersion="8" recordCount="27" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46159.444844791666" refreshedVersion="8" recordCount="27" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -887,9 +905,9 @@
     <s v="Affichage"/>
     <x v="0"/>
     <n v="90"/>
-    <n v="0"/>
-    <n v="90"/>
-    <n v="0"/>
+    <n v="80"/>
+    <n v="10"/>
+    <n v="0.88888888888888884"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -898,10 +916,10 @@
     <s v="Total generale"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="40"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
-    <n v="40"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -1006,10 +1024,10 @@
     <s v="Page d'ajout de stock de produit"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="60"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -1031,9 +1049,9 @@
     <s v="Affichage"/>
     <x v="0"/>
     <n v="40"/>
-    <n v="0"/>
     <n v="40"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -1042,10 +1060,10 @@
     <s v="Etat de Stock pour chaque clients"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="60"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -1375,7 +1393,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
@@ -1963,7 +1981,7 @@
       <c r="H16" s="6">
         <v>120</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="37">
         <f>detail_avancement!B15</f>
         <v>0</v>
       </c>
@@ -2297,7 +2315,7 @@
       <c r="H25" s="6">
         <v>60</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="37">
         <v>0</v>
       </c>
       <c r="J25" s="8">
@@ -2381,6 +2399,40 @@
       <c r="K27" s="9">
         <f>(I27/(I27+J27))</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <c r="B28" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="6">
+        <v>120</v>
+      </c>
+      <c r="I28" s="47">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
+        <f>H28-I28</f>
+        <v>120</v>
+      </c>
+      <c r="K28" s="9">
+        <f>(I28/(I28+J28))</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2423,36 +2475,36 @@
       <c r="A3" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="37">
-        <v>1750</v>
-      </c>
-      <c r="C3" s="38">
-        <v>1220</v>
-      </c>
-      <c r="D3" s="39">
-        <v>530</v>
+      <c r="B3" s="38">
+        <v>1660</v>
+      </c>
+      <c r="C3" s="39">
+        <v>1410</v>
+      </c>
+      <c r="D3" s="40">
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="43">
-        <v>1750</v>
-      </c>
-      <c r="C5" s="44">
-        <v>1220</v>
-      </c>
-      <c r="D5" s="45">
-        <v>530</v>
+      <c r="B5" s="44">
+        <v>1660</v>
+      </c>
+      <c r="C5" s="45">
+        <v>1410</v>
+      </c>
+      <c r="D5" s="46">
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2461,7 +2513,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.8493975903614458</v>
+        <v>0.7921348314606742</v>
       </c>
     </row>
   </sheetData>
@@ -2504,7 +2556,7 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1660</v>
+        <v>1780</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
@@ -2512,11 +2564,11 @@
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.8493975903614458</v>
+        <v>0.7921348314606742</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2528,7 +2580,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>4.166666666666667</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9549E906-BCBC-4614-854B-149B8B691913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A1AB27-44EA-4C07-9D12-1713FFC891A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="97">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -313,6 +313,24 @@
   </si>
   <si>
     <t>Debug generale</t>
+  </si>
+  <si>
+    <t>Gestion metier</t>
+  </si>
+  <si>
+    <t>Ajout de nouveaux ligne de etat</t>
+  </si>
+  <si>
+    <t>DashBoard</t>
+  </si>
+  <si>
+    <t>Ajouter une page statistiques qui permet d’avoir le montant total des ventes , le montant total d’achat, et le bénéfice par catégorie de produit</t>
+  </si>
+  <si>
+    <t>category-stock</t>
+  </si>
+  <si>
+    <t>Creation de tableau de produit (suivi)</t>
   </si>
 </sst>
 </file>
@@ -322,7 +340,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -417,8 +435,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +476,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -666,6 +696,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -675,9 +708,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,7 +739,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46159.444844791666" refreshedVersion="8" recordCount="27" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46161.373889814815" refreshedVersion="8" recordCount="28" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -752,7 +791,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -1066,6 +1105,18 @@
     <n v="1"/>
   </r>
   <r>
+    <s v="Backoffice"/>
+    <s v="Generale"/>
+    <s v="(------)"/>
+    <s v="Debug generale"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+    <n v="120"/>
+    <n v="0"/>
+  </r>
+  <r>
     <m/>
     <m/>
     <m/>
@@ -1393,7 +1444,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
@@ -1535,10 +1586,10 @@
         <v>34</v>
       </c>
       <c r="H4" s="6">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="I4" s="8">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="0"/>
@@ -1609,18 +1660,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="6">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I6" s="8">
         <v>120</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
@@ -1905,18 +1956,18 @@
         <v>34</v>
       </c>
       <c r="H14" s="6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I14" s="8">
         <v>80</v>
       </c>
       <c r="J14" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9">
         <f t="shared" ref="K14" si="7">(I14/(I14+J14))</f>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
@@ -1982,16 +2033,15 @@
         <v>120</v>
       </c>
       <c r="I16" s="37">
-        <f>detail_avancement!B15</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J16" s="8">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9">
         <f t="shared" ref="K16" si="9">(I16/(I16+J16))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
@@ -2128,10 +2178,10 @@
         <v>34</v>
       </c>
       <c r="H20" s="6">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="I20" s="8">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="J20" s="8">
         <f t="shared" si="4"/>
@@ -2313,18 +2363,18 @@
         <v>34</v>
       </c>
       <c r="H25" s="6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I25" s="37">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J25" s="8">
         <f t="shared" ref="J25" si="14">H25-I25</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K25" s="9">
         <f t="shared" ref="K25" si="15">(I25/(I25+J25))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
@@ -2402,6 +2452,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>27</v>
+      </c>
       <c r="B28" s="33" t="s">
         <v>15</v>
       </c>
@@ -2421,18 +2474,129 @@
         <v>34</v>
       </c>
       <c r="H28" s="6">
-        <v>120</v>
-      </c>
-      <c r="I28" s="47">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="I28" s="38">
+        <v>60</v>
       </c>
       <c r="J28" s="8">
         <f>H28-I28</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K28" s="9">
         <f>(I28/(I28+J28))</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>28</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="6">
+        <v>10</v>
+      </c>
+      <c r="I29" s="50">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8">
+        <f>H29-I29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <f>(I29/(I29+J29))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A30" s="10">
+        <v>29</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="6">
+        <v>40</v>
+      </c>
+      <c r="I30" s="50">
+        <v>40</v>
+      </c>
+      <c r="J30" s="8">
+        <f>H30-I30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <f>(I30/(I30+J30))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A31" s="52">
+        <v>30</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="6">
+        <v>20</v>
+      </c>
+      <c r="I31" s="50">
+        <v>20</v>
+      </c>
+      <c r="J31" s="8">
+        <f>H31-I31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
+        <f>(I31/(I31+J31))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2475,36 +2639,36 @@
       <c r="A3" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="38">
-        <v>1660</v>
-      </c>
-      <c r="C3" s="39">
+      <c r="B3" s="39">
+        <v>1780</v>
+      </c>
+      <c r="C3" s="40">
         <v>1410</v>
       </c>
-      <c r="D3" s="40">
-        <v>250</v>
+      <c r="D3" s="41">
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="44">
-        <v>1660</v>
-      </c>
-      <c r="C5" s="45">
+      <c r="B5" s="45">
+        <v>1780</v>
+      </c>
+      <c r="C5" s="46">
         <v>1410</v>
       </c>
-      <c r="D5" s="46">
-        <v>250</v>
+      <c r="D5" s="47">
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2513,7 +2677,7 @@
       </c>
       <c r="B12" s="13">
         <f>avancement!D2</f>
-        <v>0.7921348314606742</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2556,19 +2720,19 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="15">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1780</v>
+        <v>1930</v>
       </c>
       <c r="B2" s="15">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>1410</v>
+        <v>1930</v>
       </c>
       <c r="C2" s="15">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="D2" s="16">
         <f>(B2/(B2+C2))</f>
-        <v>0.7921348314606742</v>
+        <v>1</v>
       </c>
       <c r="E2" s="17">
         <f>((B2+C2)-A2)/A2</f>
@@ -2580,7 +2744,7 @@
       <c r="B3" s="18"/>
       <c r="C3" s="15">
         <f>C2/60</f>
-        <v>6.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>26</v>
@@ -2597,10 +2761,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
         <v>4</v>
       </c>
@@ -2608,114 +2772,391 @@
         <v>27</v>
       </c>
       <c r="C1" s="21">
-        <v>46048</v>
+        <v>46153</v>
       </c>
       <c r="D1" s="21">
-        <v>46049</v>
+        <v>46154</v>
       </c>
       <c r="E1" s="21">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="22">
+        <v>46155</v>
+      </c>
+      <c r="F1" s="21">
+        <v>46156</v>
+      </c>
+      <c r="G1" s="21">
+        <v>46157</v>
+      </c>
+      <c r="H1" s="21">
+        <v>46158</v>
+      </c>
+      <c r="I1" s="21">
+        <v>46159</v>
+      </c>
+      <c r="J1" s="21">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="15">
-        <f t="shared" ref="B2:B10" si="0">SUM(D2:P2)</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="18"/>
+        <f>SUM(C2:J2)</f>
+        <v>10</v>
+      </c>
+      <c r="C2" s="18">
+        <v>10</v>
+      </c>
       <c r="D2" s="22"/>
       <c r="E2" s="18"/>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="22">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C3" s="18"/>
+        <f>SUM(C3:J3)</f>
+        <v>60</v>
+      </c>
+      <c r="C3" s="18">
+        <v>60</v>
+      </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" s="22">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
+        <f t="shared" ref="B4:B31" si="0">SUM(C4:J4)</f>
+        <v>720</v>
+      </c>
+      <c r="C4" s="22">
+        <v>200</v>
+      </c>
+      <c r="D4" s="22">
+        <v>520</v>
+      </c>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A5" s="22">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="D5" s="18">
+        <v>30</v>
+      </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A6" s="22">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="23">
+        <v>120</v>
+      </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A7" s="22">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="D7" s="18">
+        <v>30</v>
+      </c>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A8" s="22">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="11">
+      <c r="E8" s="18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="11">
+      <c r="E9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="15">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="35">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="G16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>23</v>
+      </c>
+      <c r="B24" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>24</v>
+      </c>
+      <c r="B25" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>25</v>
+      </c>
+      <c r="B26" s="15">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="I26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>26</v>
+      </c>
+      <c r="B27" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>27</v>
+      </c>
+      <c r="B28" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>28</v>
+      </c>
+      <c r="B29" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A30" s="10">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A31" s="52">
+        <v>30</v>
+      </c>
+      <c r="B31" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Evaluation\prestashopReact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A1AB27-44EA-4C07-9D12-1713FFC891A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F1ABF1-82CD-4701-ADC1-3EBF20CF931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -699,6 +699,15 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -708,15 +717,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -739,7 +739,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46161.373889814815" refreshedVersion="8" recordCount="28" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Harena" refreshedDate="46161.556098263885" refreshedVersion="8" recordCount="31" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K993" sheet="liste des taches"/>
   </cacheSource>
@@ -770,16 +770,16 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="360"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="720"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="360"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="720"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="120"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -791,7 +791,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="31">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -823,8 +823,8 @@
     <s v="Importation fichier csv"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="360"/>
-    <n v="360"/>
+    <n v="720"/>
+    <n v="720"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -847,10 +847,10 @@
     <s v="Affichage des liste commande"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="180"/>
     <n v="120"/>
-    <n v="60"/>
-    <n v="0.66666666666666663"/>
+    <n v="120"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -943,10 +943,10 @@
     <s v="Tableau de bord (nb commande &amp; montant par jrs)"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="90"/>
     <n v="80"/>
-    <n v="10"/>
-    <n v="0.88888888888888884"/>
+    <n v="80"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Backoffice"/>
@@ -968,9 +968,9 @@
     <s v="Base"/>
     <x v="0"/>
     <n v="120"/>
-    <n v="0"/>
     <n v="120"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -1015,8 +1015,8 @@
     <s v="Recherche Multicritere (nom, categorie,intervalle de prix)"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="140"/>
-    <n v="140"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1075,10 +1075,10 @@
     <s v="Rajout d'un tableau sur l’évolution du stock journalier d’un produit"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="60"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="FrontOffice"/>
@@ -1111,10 +1111,46 @@
     <s v="Debug generale"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="120"/>
+    <n v="60"/>
+    <n v="60"/>
     <n v="0"/>
-    <n v="120"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion metier"/>
+    <s v="(------)"/>
+    <s v="Ajout de nouveaux ligne de etat"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion metier"/>
+    <s v="DashBoard"/>
+    <s v="Ajouter une page statistiques qui permet d’avoir le montant total des ventes , le montant total d’achat, et le bénéfice par catégorie de produit"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Stock"/>
+    <s v="category-stock"/>
+    <s v="Creation de tableau de produit (suivi)"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -2406,11 +2442,11 @@
         <v>40</v>
       </c>
       <c r="J26" s="8">
-        <f>H26-I26</f>
+        <f t="shared" ref="J26:J31" si="16">H26-I26</f>
         <v>0</v>
       </c>
       <c r="K26" s="9">
-        <f>(I26/(I26+J26))</f>
+        <f t="shared" ref="K26:K31" si="17">(I26/(I26+J26))</f>
         <v>1</v>
       </c>
     </row>
@@ -2443,11 +2479,11 @@
         <v>30</v>
       </c>
       <c r="J27" s="8">
-        <f>H27-I27</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K27" s="9">
-        <f>(I27/(I27+J27))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -2480,11 +2516,11 @@
         <v>60</v>
       </c>
       <c r="J28" s="8">
-        <f>H28-I28</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K28" s="9">
-        <f>(I28/(I28+J28))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -2495,13 +2531,13 @@
       <c r="B29" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="39" t="s">
         <v>92</v>
       </c>
       <c r="F29" s="7" t="s">
@@ -2513,15 +2549,15 @@
       <c r="H29" s="6">
         <v>10</v>
       </c>
-      <c r="I29" s="50">
+      <c r="I29" s="41">
         <v>10</v>
       </c>
       <c r="J29" s="8">
-        <f>H29-I29</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K29" s="9">
-        <f>(I29/(I29+J29))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -2532,13 +2568,13 @@
       <c r="B30" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="51" t="s">
+      <c r="E30" s="42" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -2550,32 +2586,32 @@
       <c r="H30" s="6">
         <v>40</v>
       </c>
-      <c r="I30" s="50">
+      <c r="I30" s="41">
         <v>40</v>
       </c>
       <c r="J30" s="8">
-        <f>H30-I30</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K30" s="9">
-        <f>(I30/(I30+J30))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A31" s="52">
+      <c r="A31" s="43">
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="42" t="s">
         <v>96</v>
       </c>
       <c r="F31" s="7" t="s">
@@ -2587,15 +2623,15 @@
       <c r="H31" s="6">
         <v>20</v>
       </c>
-      <c r="I31" s="50">
+      <c r="I31" s="41">
         <v>20</v>
       </c>
       <c r="J31" s="8">
-        <f>H31-I31</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K31" s="9">
-        <f>(I31/(I31+J31))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -2639,36 +2675,36 @@
       <c r="A3" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="39">
-        <v>1780</v>
-      </c>
-      <c r="C3" s="40">
-        <v>1410</v>
-      </c>
-      <c r="D3" s="41">
-        <v>370</v>
+      <c r="B3" s="44">
+        <v>1930</v>
+      </c>
+      <c r="C3" s="45">
+        <v>1930</v>
+      </c>
+      <c r="D3" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="45">
-        <v>1780</v>
-      </c>
-      <c r="C5" s="46">
-        <v>1410</v>
-      </c>
-      <c r="D5" s="47">
-        <v>370</v>
+      <c r="B5" s="50">
+        <v>1930</v>
+      </c>
+      <c r="C5" s="51">
+        <v>1930</v>
+      </c>
+      <c r="D5" s="52">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
@@ -2917,7 +2953,7 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="F10">
+      <c r="E10">
         <v>70</v>
       </c>
     </row>
@@ -2929,7 +2965,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="E11">
         <v>10</v>
       </c>
     </row>
@@ -2941,7 +2977,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F12">
+      <c r="E12">
         <v>10</v>
       </c>
     </row>
@@ -2993,7 +3029,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="10">
         <v>16</v>
       </c>
@@ -3005,7 +3041,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -3017,7 +3053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="10">
         <v>18</v>
       </c>
@@ -3029,7 +3065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -3041,7 +3077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -3053,7 +3089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -3065,7 +3101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="10">
         <v>22</v>
       </c>
@@ -3077,7 +3113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -3089,7 +3125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="10">
         <v>24</v>
       </c>
@@ -3104,7 +3140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -3116,49 +3152,67 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="10">
         <v>26</v>
       </c>
       <c r="B27" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+        <v>30</v>
+      </c>
+      <c r="I27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="10">
         <v>27</v>
       </c>
       <c r="B28" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+        <v>60</v>
+      </c>
+      <c r="I28">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="10">
         <v>28</v>
       </c>
       <c r="B29" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+        <f>SUM(C29:I29)</f>
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="10">
         <v>29</v>
       </c>
       <c r="B30" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="52">
+        <v>40</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A31" s="43">
         <v>30</v>
       </c>
       <c r="B31" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="J31">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
